--- a/ProjectProgress/表格/分类进展/动画问题.xlsx
+++ b/ProjectProgress/表格/分类进展/动画问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画问题" sheetId="1" r:id="R2965f687dcb4433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画问题" sheetId="1" r:id="Rd94e4812c69a459a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress2" displayName="CategoryProgress2" ref="A7:H12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress2" displayName="CategoryProgress2" ref="A7:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H21"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,A5)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIF(C8:C21,A5)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,D5)</x:f>
+        <x:f>COUNTIF(C8:C21,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,F5)</x:f>
+        <x:f>COUNTIF(C8:C21,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -520,7 +520,7 @@
         <x:v>用户备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="92" customHeight="1">
+    <x:row r="8" ht="109" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>CA-005</x:v>
       </x:c>
@@ -531,16 +531,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>最终 QA 无导入新增变形记录，但仍保留 240 条刚性骨段阈值不通过记录，均分类为源动画变化；最大骨长范围约 0.54 cm。局部缩放修正通过不等于骨长完全恒定。</x:v>
+        <x:v>旧QA240条骨段阈值事件属于已替换源动作。新Walk和NaturalIdle运行均通过独立RAW/压缩姿态范围比较，local scale保持1；新Walk仍保留源动作可变局部位移，不能据此声称骨长恒定或用户已接受伸缩。</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>确认是否接受源动作中的骨段伸缩，或明确将这些变化列为动画修复范围；当前不能直接判定为新导入损坏。</x:v>
+        <x:v>确认当前新动作的骨长变化接受标准；不将旧240条事件固定为新版本失败，独立Man库另见CA-008.02。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>46294</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>White 原动作变化与导入变形分开诊断</x:v>
+        <x:v>最新动作独立骨长范围基线与历史限制</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
@@ -579,20 +579,20 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Walk 为 30 fps、1.0667 秒循环，Idle 为 30 fps、2 秒循环，源清单的循环首尾矩阵误差为零。最终运行观察到行走和待机，未标记动画冻结；9 月 30 日换装后 30 人动画仍推进。</x:v>
+        <x:v>旧Walk/Idle循环已被新版替换：Walk第二版60fps、73帧、约1.2秒；自然Idle30fps、12秒。首尾、动画推进及压缩/源动作比较通过，30人约36秒运行保存验收有效，当前仅保留1人。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>保持这两份配套动画；脚部接触和脚滑未由本项完整覆盖，不据此添加新的修复需求。</x:v>
+        <x:v>后续按NaturalWalk第二版与NaturalIdle配套动作复核；坐姿及倚靠循环见CA-052系列。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>White 动画循环、原运行和最新换装回归</x:v>
+        <x:v>自然Idle、新Walk导入与当前单White</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
-    <x:row r="11" ht="92" customHeight="1">
+    <x:row r="11" ht="109" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>CA-004.02</x:v>
       </x:c>
@@ -603,16 +603,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>动画基准速度 68.75 cm/s，角色正常巡游 82.5 cm/s 对应 1.2 倍播放。68 次采样中所有角色速度倍率匹配，减速时也同步调整，最大速度匹配误差约 0.0000033 cm/s。</x:v>
+        <x:v>行走速度与播放倍率逻辑已迁入C++，新自然动画实例按实际地面速度推进动作时间；新Walk439采样中phase_timing和walk_timing_tracks_ground_speed通过，保留82.5cm/s巡游速度。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>后续修改巡游速度时同步核查基准速度与播放倍率。</x:v>
+        <x:v>旧68.75cm/s、1.2倍属于旧动作证据；新Walk按独立采样基线验证时间推进。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
-        <x:v>46294</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>最终速度与播放倍率逐角色验证</x:v>
+        <x:v>C++动画控制迁移与新步态运行时序</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -640,45 +640,261 @@
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-    </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="3" t="str">
+    <x:row r="13" ht="75" customHeight="1">
+      <x:c r="A13" s="7" t="str">
+        <x:v>CA-050</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>White十二秒呼吸与自然待机动作</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>miyako.blend和配套导出源已保存12秒30fps循环，加入呼吸、轻微头肩动作；源首尾位置和旋转误差为零、local scale保持1。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>当前配套待机替代旧2秒版本，循环推进见CA-004。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>blender_manifest与待机最终交付</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="7" t="str">
+        <x:v>CA-050.02</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>White行走中独立自然眨眼</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
+        <x:v>Blink_L/R已接入原生自然动画实例；约36秒454采样中30名White均眨眼，包含行走可见眨眼。后续新步态439采样复测保持。</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>30人是交付时测试样本，当前人数以CA-002为准。</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>自然待机与新步态运行gates</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="75" customHeight="1">
+      <x:c r="A15" s="7" t="str">
+        <x:v>CA-050.03</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>White原生待机行走平滑混合</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>待机和行走接入C++自然动画实例，原动作时间独立推进，观察到中间混合帧，速度与动作时间检查通过；呼吸和眨眼接入后已保存。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>播放倍率另见CA-004.02。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>自然动画实例运行混合检查</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="92" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>CA-051</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>White自然步态与落地节奏修正</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>用户反馈明显停顿后重做第二版：缩短双支撑期，平滑摆腿与落地位置/速度/加速度，减小抬脚和起伏。A_White_Walk原位替换为60fps、73帧、约1.2秒循环并保存。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>约12FPS历史实机仍影响观感，不能由动画替换推断场景性能已解决。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>用户纠正、revision2导入及最终交付</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="75" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>CA-051.02</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>White行走手指自然微蜷修正</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>针对用户指出张开手指，调整三节手指朝掌心弯曲并收拢指距及拇指，手部近景已检查，最终第二版已导入保存。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>后续动作检查配套手部姿态。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>手部反馈与第二版近景交付</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="75" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>CA-052</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>White坐下过渡动画交付</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>A_White_SitDown已由Blender导出并接入UE AdaptiveRest，原走路、呼吸和眨眼保留，最终保存引用完整。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>高度接触验收独立见CA-052.06。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>AdaptiveSit源文件与最终保存</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="75" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>CA-052.02</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>White坐姿循环待机交付</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>A_White_SeatedIdle已导入并接入坐下后循环待机；体力系统启用后仅坐稳Idle恢复体力，达到满值才结束休息。</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>体力恢复规则见CA-053.03。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>自适应坐姿与体力最新说明</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-052.03</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>White进入倚靠过渡动画交付</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>A_White_LeanEnter已导出、导入和保存，高于站立臀部高度的支撑物切换倚靠动作。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>保留真实碰撞面与支撑限制。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>AdaptiveRest倚靠过渡交付</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="75" customHeight="1">
+      <x:c r="A21" s="7" t="str">
+        <x:v>CA-052.04</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>White倚靠循环待机交付</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>A_White_LeanIdle已接入进入倚靠后循环待机，高墙实机截图和接触样本检查通过，最终动画引用完整。</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>普通自动休息周期与体力寻座规则分开判断。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>倚靠待机与最终集成记录</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B14" s="21" t="str">
+      <x:c r="B23" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C14" s="21"/>
-      <x:c r="D14" s="21"/>
-      <x:c r="E14" s="21"/>
-      <x:c r="F14" s="21"/>
-      <x:c r="G14" s="21"/>
-      <x:c r="H14" s="21"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
+      <x:c r="C23" s="21"/>
+      <x:c r="D23" s="21"/>
+      <x:c r="E23" s="21"/>
+      <x:c r="F23" s="21"/>
+      <x:c r="G23" s="21"/>
+      <x:c r="H23" s="21"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B14:H14"/>
+    <x:mergeCell ref="B23:H23"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C12">
+  <x:conditionalFormatting sqref="C8:C21">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -690,13 +906,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C12">
+    <x:dataValidation type="list" sqref="C8:C21">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ae65fcf6c4d4f23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3765f0cf4c64a3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/动画问题.xlsx
+++ b/ProjectProgress/表格/分类进展/动画问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画问题" sheetId="1" r:id="Rd94e4812c69a459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画问题" sheetId="1" r:id="R134231e4bf0740a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -568,7 +568,7 @@
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
-    <x:row r="10" ht="109" customHeight="1">
+    <x:row r="10" ht="126" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>CA-004</x:v>
       </x:c>
@@ -579,16 +579,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>旧Walk/Idle循环已被新版替换：Walk第二版60fps、73帧、约1.2秒；自然Idle30fps、12秒。首尾、动画推进及压缩/源动作比较通过，30人约36秒运行保存验收有效，当前仅保留1人。</x:v>
+        <x:v>旧Walk/Idle循环已被新版替换：Walk第二版60fps、73帧、约1.2秒；自然Idle30fps、12秒。首尾、动画推进及压缩/源动作比较通过，30人约36秒运行保存验收有效，当前150人运行已验证可见完整动画与屏外行走优化，稳定策略无失配。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>后续按NaturalWalk第二版与NaturalIdle配套动作复核；坐姿及倚靠循环见CA-052系列。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>自然Idle、新Walk导入与当前单White</x:v>
+        <x:v>自然Idle、新Walk阶段依据与150人动画策略回读</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
@@ -912,7 +912,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3765f0cf4c64a3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0ab698010e64fe1"/>
   </x:tableParts>
 </x:worksheet>
 </file>